--- a/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -7362,7 +7362,7 @@
     <t>1578</t>
   </si>
   <si>
-    <t>Centre expert maladie de Parkinson</t>
+    <t>Centre expert en maladie de Parkinson</t>
   </si>
   <si>
     <t>1579</t>

--- a/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -7788,7 +7788,7 @@
     <t>1665</t>
   </si>
   <si>
-    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins avec l'ajustement des aides optiques et nouvelles technologies dans le cadre d'handicap de la fonction visuelle (RV)</t>
+    <t>Evaluation orthoptique et/ou prise en soins avec ajustement d'aide optique et nouvelle technologie associé à un handicap de la fonction visuelle (RV)</t>
   </si>
   <si>
     <t>1666</t>

--- a/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
